--- a/Stage1-C++-Beginner/课程题目清单-入门.xlsx
+++ b/Stage1-C++-Beginner/课程题目清单-入门.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\education\events\2026\20260325入门进阶题目清单\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Stage1-C^M^M-Beginner/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D93293-FADE-4FD3-ACA5-188DE39A4121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{47432D15-673B-4B87-8DE1-2D5C72C7EF36}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="25000" xr2:uid="{47432D15-673B-4B87-8DE1-2D5C72C7EF36}"/>
   </bookViews>
   <sheets>
     <sheet name="入门" sheetId="1" r:id="rId1"/>
@@ -2644,11 +2644,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2670,7 +2670,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2697,7 +2697,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2787,14 +2787,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2802,15 +2808,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{E0B74BDF-60E4-42FA-9E2C-ECC37A4B3788}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2827,7 +2827,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3144,17 +3144,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1A565B-B6AB-4E1D-ABEA-CE21B80AE16C}">
   <dimension ref="A1:E143"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.21875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="36.21875" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="13.1640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3171,2170 +3171,2170 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>2789</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="1:5" ht="16">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>1077</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    <row r="4" spans="1:5" ht="16">
+      <c r="A4" s="7"/>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>1078</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="1:5" ht="16">
+      <c r="A5" s="7"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>1084</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    <row r="6" spans="1:5" ht="16">
+      <c r="A6" s="7"/>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>1085</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3" t="s">
+    <row r="7" spans="1:5" ht="16">
+      <c r="A7" s="7"/>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>1098</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:5" ht="16">
+      <c r="A8" s="7"/>
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>1099</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="1:5" ht="16">
+      <c r="A9" s="7"/>
+      <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>1100</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:5" ht="16">
+      <c r="A10" s="8"/>
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>1109</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>2790</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="3" t="s">
+    <row r="12" spans="1:5" ht="16">
+      <c r="A12" s="7"/>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>2741</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="s">
+    <row r="13" spans="1:5" ht="16">
+      <c r="A13" s="7"/>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>2743</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="3" t="s">
+    <row r="14" spans="1:5" ht="16">
+      <c r="A14" s="7"/>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>1082</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
+    <row r="15" spans="1:5" ht="16">
+      <c r="A15" s="7"/>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>1105</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="3" t="s">
+    <row r="16" spans="1:5" ht="16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>1104</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="1:5" ht="16">
+      <c r="A17" s="7"/>
+      <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>1080</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="1:5" ht="16">
+      <c r="A18" s="7"/>
+      <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>1102</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="1:5" ht="16">
+      <c r="A19" s="7"/>
+      <c r="B19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>1101</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:5" ht="16">
+      <c r="A20" s="7"/>
+      <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <v>1110</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="1:5" ht="16">
+      <c r="A21" s="7"/>
+      <c r="B21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>1108</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="1:5" ht="16">
+      <c r="A22" s="7"/>
+      <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>1111</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="1:5" ht="16">
+      <c r="A23" s="8"/>
+      <c r="B23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>1086</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="2">
         <v>2791</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="3" t="s">
+    <row r="25" spans="1:5" ht="16">
+      <c r="A25" s="7"/>
+      <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="2">
         <v>2701</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="3" t="s">
+    <row r="26" spans="1:5" ht="16">
+      <c r="A26" s="7"/>
+      <c r="B26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="2">
         <v>2745</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3" t="s">
+    <row r="27" spans="1:5" ht="16">
+      <c r="A27" s="7"/>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="2">
         <v>1117</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3" t="s">
+    <row r="28" spans="1:5" ht="16">
+      <c r="A28" s="7"/>
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="2">
         <v>1119</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="3" t="s">
+    <row r="29" spans="1:5" ht="16">
+      <c r="A29" s="7"/>
+      <c r="B29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>1121</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="3" t="s">
+    <row r="30" spans="1:5" ht="16">
+      <c r="A30" s="7"/>
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="2">
         <v>1122</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="1:5" ht="16">
+      <c r="A31" s="7"/>
+      <c r="B31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="2">
         <v>1118</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="1:5" ht="16">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>1123</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="1:5" ht="16">
+      <c r="A33" s="7"/>
+      <c r="B33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="2">
         <v>1124</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="1:5" ht="16">
+      <c r="A34" s="7"/>
+      <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="2">
         <v>1120</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="1:5" ht="16">
+      <c r="A35" s="7"/>
+      <c r="B35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="2">
         <v>1125</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="3" t="s">
+    <row r="36" spans="1:5" ht="16">
+      <c r="A36" s="7"/>
+      <c r="B36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="2">
         <v>1136</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="3" t="s">
+    <row r="37" spans="1:5" ht="16">
+      <c r="A37" s="8"/>
+      <c r="B37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="2">
         <v>1126</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A38" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="2">
         <v>2792</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="3" t="s">
+    <row r="39" spans="1:5" ht="16">
+      <c r="A39" s="7"/>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="2">
         <v>2746</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="3" t="s">
+    <row r="40" spans="1:5" ht="16">
+      <c r="A40" s="7"/>
+      <c r="B40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="2">
         <v>2721</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="3" t="s">
+    <row r="41" spans="1:5" ht="16">
+      <c r="A41" s="7"/>
+      <c r="B41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="2">
         <v>1137</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="3" t="s">
+    <row r="42" spans="1:5" ht="16">
+      <c r="A42" s="7"/>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="2">
         <v>1127</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="3" t="s">
+    <row r="43" spans="1:5" ht="16">
+      <c r="A43" s="7"/>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="2">
         <v>1133</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="3" t="s">
+    <row r="44" spans="1:5" ht="16">
+      <c r="A44" s="7"/>
+      <c r="B44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="2">
         <v>1134</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="3" t="s">
+    <row r="45" spans="1:5" ht="16">
+      <c r="A45" s="7"/>
+      <c r="B45" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="2">
         <v>2503</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
-      <c r="B46" s="3" t="s">
+    <row r="46" spans="1:5" ht="16">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="2">
         <v>1132</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
-      <c r="B47" s="3" t="s">
+    <row r="47" spans="1:5" ht="16">
+      <c r="A47" s="7"/>
+      <c r="B47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="2">
         <v>1141</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-      <c r="B48" s="3" t="s">
+    <row r="48" spans="1:5" ht="16">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="2">
         <v>2504</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A49" s="5"/>
-      <c r="B49" s="3" t="s">
+    <row r="49" spans="1:5" ht="16">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="2">
         <v>2491</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A50" s="6"/>
-      <c r="B50" s="3" t="s">
+    <row r="50" spans="1:5" ht="16">
+      <c r="A50" s="8"/>
+      <c r="B50" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2">
         <v>2487</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A51" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="2">
         <v>2793</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
-      <c r="B52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="3" t="s">
+    <row r="52" spans="1:5" ht="16">
+      <c r="A52" s="7"/>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="2">
         <v>2750</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A53" s="5"/>
-      <c r="B53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="3" t="s">
+    <row r="53" spans="1:5" ht="16">
+      <c r="A53" s="7"/>
+      <c r="B53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="2">
         <v>2751</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="5"/>
-      <c r="B54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="3" t="s">
+    <row r="54" spans="1:5" ht="16">
+      <c r="A54" s="7"/>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="2">
         <v>1153</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="5"/>
-      <c r="B55" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="3" t="s">
+    <row r="55" spans="1:5" ht="16">
+      <c r="A55" s="7"/>
+      <c r="B55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="2">
         <v>2695</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="5"/>
-      <c r="B56" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="3" t="s">
+    <row r="56" spans="1:5" ht="16">
+      <c r="A56" s="7"/>
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="2">
         <v>1144</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
-      <c r="B57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="3" t="s">
+    <row r="57" spans="1:5" ht="16">
+      <c r="A57" s="7"/>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="2">
         <v>9528</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="5"/>
-      <c r="B58" s="3" t="s">
+    <row r="58" spans="1:5" ht="16">
+      <c r="A58" s="7"/>
+      <c r="B58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="2">
         <v>1148</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
-      <c r="B59" s="3" t="s">
+    <row r="59" spans="1:5" ht="16">
+      <c r="A59" s="7"/>
+      <c r="B59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="2">
         <v>1145</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
-      <c r="B60" s="3" t="s">
+    <row r="60" spans="1:5" ht="16">
+      <c r="A60" s="7"/>
+      <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="2">
         <v>1149</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="3" t="s">
+    <row r="61" spans="1:5" ht="16">
+      <c r="A61" s="7"/>
+      <c r="B61" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="2">
         <v>1147</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
-      <c r="B62" s="3" t="s">
+    <row r="62" spans="1:5" ht="16">
+      <c r="A62" s="7"/>
+      <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="2">
         <v>1150</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="6"/>
-      <c r="B63" s="3" t="s">
+    <row r="63" spans="1:5" ht="16">
+      <c r="A63" s="8"/>
+      <c r="B63" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3">
+      <c r="C63" s="2"/>
+      <c r="D63" s="2">
         <v>1151</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A64" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="2">
         <v>2794</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="5"/>
-      <c r="B65" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="3" t="s">
+    <row r="65" spans="1:5" ht="16">
+      <c r="A65" s="7"/>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="2">
         <v>2753</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="5"/>
-      <c r="B66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="3" t="s">
+    <row r="66" spans="1:5" ht="16">
+      <c r="A66" s="7"/>
+      <c r="B66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="2">
         <v>2748</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A67" s="5"/>
-      <c r="B67" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C67" s="3" t="s">
+    <row r="67" spans="1:5" ht="16">
+      <c r="A67" s="7"/>
+      <c r="B67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="2">
         <v>1255</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A68" s="5"/>
-      <c r="B68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="3" t="s">
+    <row r="68" spans="1:5" ht="16">
+      <c r="A68" s="7"/>
+      <c r="B68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="2">
         <v>9384</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
-      <c r="B69" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="3" t="s">
+    <row r="69" spans="1:5" ht="16">
+      <c r="A69" s="7"/>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="2">
         <v>1335</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="5"/>
-      <c r="B70" s="3" t="s">
+    <row r="70" spans="1:5" ht="16">
+      <c r="A70" s="7"/>
+      <c r="B70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="2">
         <v>3166</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="5"/>
-      <c r="B71" s="3" t="s">
+    <row r="71" spans="1:5" ht="16">
+      <c r="A71" s="7"/>
+      <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="2">
         <v>1154</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A72" s="5"/>
-      <c r="B72" s="3" t="s">
+    <row r="72" spans="1:5" ht="16">
+      <c r="A72" s="7"/>
+      <c r="B72" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="2">
         <v>1189</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A73" s="5"/>
-      <c r="B73" s="3" t="s">
+    <row r="73" spans="1:5" ht="16">
+      <c r="A73" s="7"/>
+      <c r="B73" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="2">
         <v>2481</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A74" s="5"/>
-      <c r="B74" s="3" t="s">
+    <row r="74" spans="1:5" ht="16">
+      <c r="A74" s="7"/>
+      <c r="B74" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="2">
         <v>1164</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A75" s="6"/>
-      <c r="B75" s="3" t="s">
+    <row r="75" spans="1:5" ht="16">
+      <c r="A75" s="8"/>
+      <c r="B75" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="2">
         <v>1174</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A76" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="2">
         <v>2795</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="3" t="s">
+    <row r="77" spans="1:5" ht="16">
+      <c r="A77" s="7"/>
+      <c r="B77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="2">
         <v>2757</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="5"/>
-      <c r="B78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="3" t="s">
+    <row r="78" spans="1:5" ht="16">
+      <c r="A78" s="7"/>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="2">
         <v>3242</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A79" s="5"/>
-      <c r="B79" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="3" t="s">
+    <row r="79" spans="1:5" ht="16">
+      <c r="A79" s="7"/>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="2">
         <v>9426</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E79" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="5"/>
-      <c r="B80" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="3" t="s">
+    <row r="80" spans="1:5" ht="16">
+      <c r="A80" s="7"/>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80" s="2">
         <v>3165</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A81" s="5"/>
-      <c r="B81" s="3" t="s">
+    <row r="81" spans="1:5" ht="16">
+      <c r="A81" s="7"/>
+      <c r="B81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="2">
         <v>1197</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="5"/>
-      <c r="B82" s="3" t="s">
+    <row r="82" spans="1:5" ht="16">
+      <c r="A82" s="7"/>
+      <c r="B82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="2">
         <v>2170</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E82" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A83" s="5"/>
-      <c r="B83" s="3" t="s">
+    <row r="83" spans="1:5" ht="16">
+      <c r="A83" s="7"/>
+      <c r="B83" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="2">
         <v>1195</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A84" s="5"/>
-      <c r="B84" s="3" t="s">
+    <row r="84" spans="1:5" ht="16">
+      <c r="A84" s="7"/>
+      <c r="B84" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="2">
         <v>1196</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E84" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A85" s="5"/>
-      <c r="B85" s="3" t="s">
+    <row r="85" spans="1:5" ht="16">
+      <c r="A85" s="7"/>
+      <c r="B85" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="2">
         <v>1270</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A86" s="5"/>
-      <c r="B86" s="3" t="s">
+    <row r="86" spans="1:5" ht="16">
+      <c r="A86" s="7"/>
+      <c r="B86" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="2">
         <v>1178</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E86" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A87" s="6"/>
-      <c r="B87" s="3" t="s">
+    <row r="87" spans="1:5" ht="16">
+      <c r="A87" s="8"/>
+      <c r="B87" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="2">
         <v>3179</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="E87" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+    <row r="88" spans="1:5" ht="15.5" customHeight="1">
+      <c r="A88" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="3" t="s">
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="2">
         <v>2702</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E88" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A89" s="5"/>
-      <c r="B89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="3" t="s">
+    <row r="89" spans="1:5" ht="16">
+      <c r="A89" s="7"/>
+      <c r="B89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="2">
         <v>2754</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A90" s="5"/>
-      <c r="B90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="3" t="s">
+    <row r="90" spans="1:5" ht="16">
+      <c r="A90" s="7"/>
+      <c r="B90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="2">
         <v>1152</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E90" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A91" s="5"/>
-      <c r="B91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="3" t="s">
+    <row r="91" spans="1:5" ht="16">
+      <c r="A91" s="7"/>
+      <c r="B91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="2">
         <v>2480</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A92" s="5"/>
-      <c r="B92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="3" t="s">
+    <row r="92" spans="1:5" ht="16">
+      <c r="A92" s="7"/>
+      <c r="B92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="2">
         <v>2515</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="E92" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A93" s="5"/>
-      <c r="B93" s="3" t="s">
+    <row r="93" spans="1:5" ht="16">
+      <c r="A93" s="7"/>
+      <c r="B93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D93" s="2">
         <v>1160</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="E93" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A94" s="5"/>
-      <c r="B94" s="3" t="s">
+    <row r="94" spans="1:5" ht="16">
+      <c r="A94" s="7"/>
+      <c r="B94" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="2">
         <v>2684</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="E94" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A95" s="5"/>
-      <c r="B95" s="3" t="s">
+    <row r="95" spans="1:5" ht="16">
+      <c r="A95" s="7"/>
+      <c r="B95" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D95" s="2">
         <v>1155</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="E95" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A96" s="5"/>
-      <c r="B96" s="3" t="s">
+    <row r="96" spans="1:5" ht="16">
+      <c r="A96" s="7"/>
+      <c r="B96" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="2">
         <v>1167</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="E96" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A97" s="5"/>
-      <c r="B97" s="3" t="s">
+    <row r="97" spans="1:5" ht="16">
+      <c r="A97" s="7"/>
+      <c r="B97" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="2">
         <v>2681</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="E97" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A98" s="5"/>
-      <c r="B98" s="3" t="s">
+    <row r="98" spans="1:5" ht="16">
+      <c r="A98" s="7"/>
+      <c r="B98" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="2">
         <v>1128</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="E98" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A99" s="6"/>
-      <c r="B99" s="3" t="s">
+    <row r="99" spans="1:5" ht="16">
+      <c r="A99" s="8"/>
+      <c r="B99" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="2">
         <v>2112</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E99" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+    <row r="100" spans="1:5" ht="16">
+      <c r="A100" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="2">
         <v>2796</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E100" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A101" s="5"/>
-      <c r="B101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" s="3" t="s">
+    <row r="101" spans="1:5" ht="16">
+      <c r="A101" s="7"/>
+      <c r="B101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="2">
         <v>2749</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="E101" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A102" s="5"/>
-      <c r="B102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C102" s="3" t="s">
+    <row r="102" spans="1:5" ht="16">
+      <c r="A102" s="7"/>
+      <c r="B102" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="2">
         <v>2656</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="E102" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A103" s="5"/>
-      <c r="B103" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" s="3" t="s">
+    <row r="103" spans="1:5" ht="16">
+      <c r="A103" s="7"/>
+      <c r="B103" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D103" s="2">
         <v>1299</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="E103" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A104" s="5"/>
-      <c r="B104" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C104" s="3" t="s">
+    <row r="104" spans="1:5" ht="16">
+      <c r="A104" s="7"/>
+      <c r="B104" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="2">
         <v>1293</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E104" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A105" s="5"/>
-      <c r="B105" s="3" t="s">
+    <row r="105" spans="1:5" ht="16">
+      <c r="A105" s="7"/>
+      <c r="B105" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105" s="2">
         <v>1252</v>
       </c>
-      <c r="E105" s="4" t="s">
+      <c r="E105" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A106" s="5"/>
-      <c r="B106" s="3" t="s">
+    <row r="106" spans="1:5" ht="16">
+      <c r="A106" s="7"/>
+      <c r="B106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="2">
         <v>1286</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E106" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A107" s="5"/>
-      <c r="B107" s="3" t="s">
+    <row r="107" spans="1:5" ht="16">
+      <c r="A107" s="7"/>
+      <c r="B107" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="2">
         <v>2482</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="E107" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A108" s="5"/>
-      <c r="B108" s="3" t="s">
+    <row r="108" spans="1:5" ht="16">
+      <c r="A108" s="7"/>
+      <c r="B108" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="2">
         <v>2495</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E108" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A109" s="5"/>
-      <c r="B109" s="3" t="s">
+    <row r="109" spans="1:5" ht="16">
+      <c r="A109" s="7"/>
+      <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="2">
         <v>1294</v>
       </c>
-      <c r="E109" s="4" t="s">
+      <c r="E109" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A110" s="5"/>
-      <c r="B110" s="3" t="s">
+    <row r="110" spans="1:5" ht="16">
+      <c r="A110" s="7"/>
+      <c r="B110" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="2">
         <v>1338</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A111" s="6"/>
-      <c r="B111" s="3" t="s">
+    <row r="111" spans="1:5" ht="16">
+      <c r="A111" s="8"/>
+      <c r="B111" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D111" s="2">
         <v>1300</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E111" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+    <row r="112" spans="1:5" ht="16">
+      <c r="A112" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B112" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" s="3" t="s">
+      <c r="B112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="2">
         <v>2704</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E112" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A113" s="5"/>
-      <c r="B113" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C113" s="3" t="s">
+    <row r="113" spans="1:5" ht="16">
+      <c r="A113" s="7"/>
+      <c r="B113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113" s="2">
         <v>1250</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="E113" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A114" s="5"/>
-      <c r="B114" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C114" s="3" t="s">
+    <row r="114" spans="1:5" ht="16">
+      <c r="A114" s="7"/>
+      <c r="B114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="2">
         <v>2533</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E114" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A115" s="5"/>
-      <c r="B115" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C115" s="3" t="s">
+    <row r="115" spans="1:5" ht="16">
+      <c r="A115" s="7"/>
+      <c r="B115" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115" s="2">
         <v>2484</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="E115" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A116" s="5"/>
-      <c r="B116" s="3" t="s">
+    <row r="116" spans="1:5" ht="16">
+      <c r="A116" s="7"/>
+      <c r="B116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="2">
         <v>1199</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="E116" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A117" s="5"/>
-      <c r="B117" s="3" t="s">
+    <row r="117" spans="1:5" ht="16">
+      <c r="A117" s="7"/>
+      <c r="B117" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="2">
         <v>1248</v>
       </c>
-      <c r="E117" s="4" t="s">
+      <c r="E117" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A118" s="5"/>
-      <c r="B118" s="3" t="s">
+    <row r="118" spans="1:5" ht="16">
+      <c r="A118" s="7"/>
+      <c r="B118" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D118" s="2">
         <v>1203</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="E118" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A119" s="5"/>
-      <c r="B119" s="3" t="s">
+    <row r="119" spans="1:5" ht="16">
+      <c r="A119" s="7"/>
+      <c r="B119" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="2">
         <v>2682</v>
       </c>
-      <c r="E119" s="4" t="s">
+      <c r="E119" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A120" s="5"/>
-      <c r="B120" s="3" t="s">
+    <row r="120" spans="1:5" ht="16">
+      <c r="A120" s="7"/>
+      <c r="B120" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="2">
         <v>2683</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="E120" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A121" s="5"/>
-      <c r="B121" s="3" t="s">
+    <row r="121" spans="1:5" ht="16">
+      <c r="A121" s="7"/>
+      <c r="B121" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D121" s="3">
+      <c r="D121" s="2">
         <v>3167</v>
       </c>
-      <c r="E121" s="4" t="s">
+      <c r="E121" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A122" s="6"/>
-      <c r="B122" s="3" t="s">
+    <row r="122" spans="1:5" ht="16">
+      <c r="A122" s="8"/>
+      <c r="B122" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122" s="2">
         <v>3171</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E122" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
+    <row r="123" spans="1:5" ht="16">
+      <c r="A123" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123" s="2">
         <v>2797</v>
       </c>
-      <c r="E123" s="4" t="s">
+      <c r="E123" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A124" s="5"/>
-      <c r="B124" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="3" t="s">
+    <row r="124" spans="1:5" ht="16">
+      <c r="A124" s="7"/>
+      <c r="B124" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="2">
         <v>1321</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="E124" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A125" s="5"/>
-      <c r="B125" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125" s="3" t="s">
+    <row r="125" spans="1:5" ht="16">
+      <c r="A125" s="7"/>
+      <c r="B125" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125" s="2">
         <v>3192</v>
       </c>
-      <c r="E125" s="4" t="s">
+      <c r="E125" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A126" s="5"/>
-      <c r="B126" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C126" s="3" t="s">
+    <row r="126" spans="1:5" ht="16">
+      <c r="A126" s="7"/>
+      <c r="B126" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126" s="2">
         <v>1336</v>
       </c>
-      <c r="E126" s="4" t="s">
+      <c r="E126" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A127" s="5"/>
-      <c r="B127" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C127" s="3" t="s">
+    <row r="127" spans="1:5" ht="16">
+      <c r="A127" s="7"/>
+      <c r="B127" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D127" s="3">
+      <c r="D127" s="2">
         <v>1323</v>
       </c>
-      <c r="E127" s="4" t="s">
+      <c r="E127" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A128" s="5"/>
-      <c r="B128" s="3" t="s">
+    <row r="128" spans="1:5" ht="16">
+      <c r="A128" s="7"/>
+      <c r="B128" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="C128" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128" s="2">
         <v>3191</v>
       </c>
-      <c r="E128" s="4" t="s">
+      <c r="E128" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A129" s="5"/>
-      <c r="B129" s="3" t="s">
+    <row r="129" spans="1:5" ht="16">
+      <c r="A129" s="7"/>
+      <c r="B129" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D129" s="3">
+      <c r="D129" s="2">
         <v>3190</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="E129" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A130" s="5"/>
-      <c r="B130" s="3" t="s">
+    <row r="130" spans="1:5" ht="16">
+      <c r="A130" s="7"/>
+      <c r="B130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130" s="2">
         <v>2498</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="E130" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A131" s="5"/>
-      <c r="B131" s="3" t="s">
+    <row r="131" spans="1:5" ht="16">
+      <c r="A131" s="7"/>
+      <c r="B131" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D131" s="2">
         <v>1333</v>
       </c>
-      <c r="E131" s="4" t="s">
+      <c r="E131" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A132" s="6"/>
-      <c r="B132" s="3" t="s">
+    <row r="132" spans="1:5" ht="16">
+      <c r="A132" s="8"/>
+      <c r="B132" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D132" s="2">
         <v>5177</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="E132" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A133" s="2" t="s">
+    <row r="133" spans="1:5" ht="16">
+      <c r="A133" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" s="3" t="s">
+      <c r="B133" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133" s="2">
         <v>2703</v>
       </c>
-      <c r="E133" s="4" t="s">
+      <c r="E133" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A134" s="5"/>
-      <c r="B134" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C134" s="3" t="s">
+    <row r="134" spans="1:5" ht="16">
+      <c r="A134" s="7"/>
+      <c r="B134" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="2">
         <v>2640</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E134" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A135" s="5"/>
-      <c r="B135" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C135" s="3" t="s">
+    <row r="135" spans="1:5" ht="16">
+      <c r="A135" s="7"/>
+      <c r="B135" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="2">
         <v>2657</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="E135" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A136" s="5"/>
-      <c r="B136" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C136" s="3" t="s">
+    <row r="136" spans="1:5" ht="16">
+      <c r="A136" s="7"/>
+      <c r="B136" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="2">
         <v>2113</v>
       </c>
-      <c r="E136" s="4" t="s">
+      <c r="E136" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A137" s="5"/>
-      <c r="B137" s="3" t="s">
+    <row r="137" spans="1:5" ht="16">
+      <c r="A137" s="7"/>
+      <c r="B137" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137" s="2">
         <v>2658</v>
       </c>
-      <c r="E137" s="4" t="s">
+      <c r="E137" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A138" s="5"/>
-      <c r="B138" s="3" t="s">
+    <row r="138" spans="1:5" ht="16">
+      <c r="A138" s="7"/>
+      <c r="B138" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138" s="2">
         <v>1292</v>
       </c>
-      <c r="E138" s="4" t="s">
+      <c r="E138" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A139" s="5"/>
-      <c r="B139" s="3" t="s">
+    <row r="139" spans="1:5" ht="16">
+      <c r="A139" s="7"/>
+      <c r="B139" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D139" s="3">
+      <c r="D139" s="2">
         <v>2162</v>
       </c>
-      <c r="E139" s="4" t="s">
+      <c r="E139" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A140" s="5"/>
-      <c r="B140" s="3" t="s">
+    <row r="140" spans="1:5" ht="16">
+      <c r="A140" s="7"/>
+      <c r="B140" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140" s="2">
         <v>1177</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="E140" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A141" s="5"/>
-      <c r="B141" s="3" t="s">
+    <row r="141" spans="1:5" ht="16">
+      <c r="A141" s="7"/>
+      <c r="B141" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D141" s="3">
+      <c r="D141" s="2">
         <v>2496</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E141" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A142" s="5"/>
-      <c r="B142" s="3" t="s">
+    <row r="142" spans="1:5" ht="16">
+      <c r="A142" s="7"/>
+      <c r="B142" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142" s="2">
         <v>1173</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E142" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A143" s="6"/>
-      <c r="B143" s="3" t="s">
+    <row r="143" spans="1:5" ht="16">
+      <c r="A143" s="8"/>
+      <c r="B143" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D143" s="3">
+      <c r="D143" s="2">
         <v>2689</v>
       </c>
-      <c r="E143" s="4" t="s">
+      <c r="E143" s="3" t="s">
         <v>59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A51:A63"/>
+    <mergeCell ref="A64:A75"/>
+    <mergeCell ref="A38:A50"/>
+    <mergeCell ref="A11:A23"/>
+    <mergeCell ref="A24:A37"/>
     <mergeCell ref="A100:A111"/>
     <mergeCell ref="A112:A122"/>
     <mergeCell ref="A123:A132"/>
     <mergeCell ref="A133:A143"/>
     <mergeCell ref="A76:A87"/>
     <mergeCell ref="A88:A99"/>
-    <mergeCell ref="A51:A63"/>
-    <mergeCell ref="A64:A75"/>
-    <mergeCell ref="A38:A50"/>
-    <mergeCell ref="A11:A23"/>
-    <mergeCell ref="A24:A37"/>
-    <mergeCell ref="A2:A10"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
